--- a/results/Int All Data 0.3/Linea_fi_explain.xlsx
+++ b/results/Int All Data 0.3/Linea_fi_explain.xlsx
@@ -1685,7 +1685,7 @@
         <v>-0.001222248500097155</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0007709659144662884</v>
+        <v>-0.0007712540618667806</v>
       </c>
       <c r="F3" t="n">
         <v>-1.078610663516324e-05</v>
@@ -1694,7 +1694,7 @@
         <v>0.05553967691364157</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006798631044027935</v>
+        <v>0.006802694432894249</v>
       </c>
       <c r="I3" t="n">
         <v>0.0004823798174734183</v>
@@ -1883,7 +1883,7 @@
         <v>0.01885537612156736</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.002791166475855309</v>
+        <v>0.002782906695885344</v>
       </c>
       <c r="BT3" t="n">
         <v>-0.001277226811346357</v>
@@ -1892,7 +1892,7 @@
         <v>0.007502020500570587</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0007275758676700662</v>
+        <v>-0.0007315790702321158</v>
       </c>
       <c r="BW3" t="n">
         <v>-5.580352854786975e-05</v>
@@ -1901,19 +1901,19 @@
         <v>0.00445042446843602</v>
       </c>
       <c r="BY3" t="n">
+        <v>0.000660915823875361</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>0.0006651423665634427</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0.0006650772887109823</v>
       </c>
       <c r="CA3" t="n">
         <v>0.002756271847512377</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.02161472923577595</v>
+        <v>0.02160216087728753</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.0009107408406167571</v>
+        <v>-0.0009107603011151309</v>
       </c>
       <c r="CD3" t="n">
         <v>0.0006783807374175054</v>
@@ -1922,7 +1922,7 @@
         <v>-0.0003963853555843488</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0002863432818113199</v>
+        <v>-0.0002781472071318703</v>
       </c>
       <c r="CG3" t="n">
         <v>0.4245436797532737</v>
@@ -1934,7 +1934,7 @@
         <v>0.2910689813152925</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-5.580352854786975e-05</v>
+        <v>-6.001938014989383e-05</v>
       </c>
       <c r="CK3" t="n">
         <v>0.002020200387120472</v>
@@ -2015,7 +2015,7 @@
         <v>0.01493407442109877</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.007025713092938151</v>
+        <v>0.007029909484041801</v>
       </c>
       <c r="DL3" t="n">
         <v>-0.0006286520789471695</v>
@@ -2027,10 +2027,10 @@
         <v>0.01096288118667747</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.01552386782899448</v>
+        <v>0.01552806422009813</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.004780582738026731</v>
+        <v>0.004776379291200335</v>
       </c>
       <c r="DQ3" t="n">
         <v>-8.092286483719958e-05</v>
@@ -2054,7 +2054,7 @@
         <v>0.001562130666844489</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.002541482007665448</v>
+        <v>0.002537266156063423</v>
       </c>
       <c r="DY3" t="n">
         <v>-0.003458733474370057</v>
@@ -2066,7 +2066,7 @@
         <v>0.01313475352311298</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.01552400083123181</v>
+        <v>0.01551980444012816</v>
       </c>
       <c r="EC3" t="n">
         <v>0.004403792039155375</v>
@@ -2111,7 +2111,7 @@
         <v>0.000293615552961588</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.003427038177365839</v>
+        <v>0.003422841786262189</v>
       </c>
       <c r="ER3" t="n">
         <v>0.0005324235275452449</v>
@@ -2120,7 +2120,7 @@
         <v>-0.000234095073616759</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.002063372776839686</v>
+        <v>-0.002067599319527766</v>
       </c>
       <c r="EU3" t="n">
         <v>0.05637676136446114</v>
@@ -2154,7 +2154,7 @@
         <v>0.002118233451771197</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002491044856039269</v>
+        <v>0.00248830055850972</v>
       </c>
       <c r="F4" t="n">
         <v>0.001761671530261677</v>
@@ -2163,7 +2163,7 @@
         <v>0.056422644362517</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01222296566788377</v>
+        <v>0.01222523388388683</v>
       </c>
       <c r="I4" t="n">
         <v>0.003906207434074245</v>
@@ -2352,7 +2352,7 @@
         <v>0.03378210047326245</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.01202328703260688</v>
+        <v>0.01201629788289154</v>
       </c>
       <c r="BT4" t="n">
         <v>0.004286372555520383</v>
@@ -2361,7 +2361,7 @@
         <v>0.01673643569914616</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0049340337037631</v>
+        <v>0.004940499263971306</v>
       </c>
       <c r="BW4" t="n">
         <v>0.0002156286409638051</v>
@@ -2370,19 +2370,19 @@
         <v>0.006308671754487597</v>
       </c>
       <c r="BY4" t="n">
+        <v>0.001117590492875064</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>0.00112074958622075</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.001119064739449485</v>
       </c>
       <c r="CA4" t="n">
         <v>0.01030016141323904</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0246444208737049</v>
+        <v>0.02464807910403841</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.004040083377787164</v>
+        <v>0.004050313174190196</v>
       </c>
       <c r="CD4" t="n">
         <v>0.005279324499846449</v>
@@ -2391,7 +2391,7 @@
         <v>0.004218157537757395</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003476730402592151</v>
+        <v>0.003478126234603662</v>
       </c>
       <c r="CG4" t="n">
         <v>0.1309495582021393</v>
@@ -2403,7 +2403,7 @@
         <v>0.1113117740781854</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0002156286409638051</v>
+        <v>0.0002120512969695175</v>
       </c>
       <c r="CK4" t="n">
         <v>0.009612439779312724</v>
@@ -2484,7 +2484,7 @@
         <v>0.02547245311758727</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.01372302898960947</v>
+        <v>0.01373179526474035</v>
       </c>
       <c r="DL4" t="n">
         <v>0.0009642789070162112</v>
@@ -2496,10 +2496,10 @@
         <v>0.03092859065023762</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.03541551127228954</v>
+        <v>0.03542019883729156</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.007529010637945818</v>
+        <v>0.007527763611511332</v>
       </c>
       <c r="DQ4" t="n">
         <v>0.0008254186060673931</v>
@@ -2523,7 +2523,7 @@
         <v>0.003883067899416475</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.01108684426946947</v>
+        <v>0.01108805070180472</v>
       </c>
       <c r="DY4" t="n">
         <v>0.01648459593973328</v>
@@ -2535,7 +2535,7 @@
         <v>0.04169150138033845</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.03542195253165049</v>
+        <v>0.03541726466381223</v>
       </c>
       <c r="EC4" t="n">
         <v>0.01067433257517316</v>
@@ -2580,7 +2580,7 @@
         <v>0.000807396037092823</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.008522453480387165</v>
+        <v>0.0085098425675913</v>
       </c>
       <c r="ER4" t="n">
         <v>0.001263672018198968</v>
@@ -2589,7 +2589,7 @@
         <v>0.001341544382120561</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.01737114033759892</v>
+        <v>0.0173617184192119</v>
       </c>
       <c r="EU4" t="n">
         <v>0.07388164753045062</v>
@@ -2851,7 +2851,7 @@
         <v>-0.006956155143338949</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.007209106239460384</v>
+        <v>-0.007251264755480625</v>
       </c>
       <c r="CD5" t="n">
         <v>-0.005842791088692745</v>
@@ -3561,7 +3561,7 @@
         <v>-0.0006096986801715609</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.001463867783970852</v>
+        <v>-0.001484832144557852</v>
       </c>
       <c r="F7" t="n">
         <v>-9.292391334499996e-05</v>
@@ -3780,7 +3780,7 @@
         <v>0.001108892099582509</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.001129699423760616</v>
+        <v>0.001108892099582509</v>
       </c>
       <c r="CA7" t="n">
         <v>0.001411099455436532</v>
@@ -3798,7 +3798,7 @@
         <v>-0.0005401991172630461</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0002277629231267564</v>
+        <v>0.0002570204020077849</v>
       </c>
       <c r="CG7" t="n">
         <v>0.4239373252236904</v>
@@ -3930,7 +3930,7 @@
         <v>0.00130667405324435</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.0002288225833971369</v>
+        <v>-0.0002499018414072574</v>
       </c>
       <c r="DY7" t="n">
         <v>3.436522278704713e-06</v>
@@ -4039,7 +4039,7 @@
         <v>0.06797974251164003</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01550483812689874</v>
+        <v>0.01551499659906453</v>
       </c>
       <c r="I8" t="n">
         <v>0.001847551652415496</v>
@@ -4228,7 +4228,7 @@
         <v>0.02689502611819659</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.008307191664225338</v>
+        <v>0.008275718730947961</v>
       </c>
       <c r="BT8" t="n">
         <v>0.0002496878901372928</v>
@@ -4255,10 +4255,10 @@
         <v>0.01172193600028741</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.03951350435792957</v>
+        <v>0.0394822933716624</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001573329955106503</v>
+        <v>0.00160480288838388</v>
       </c>
       <c r="CD8" t="n">
         <v>0.0006294927686853746</v>
@@ -4267,7 +4267,7 @@
         <v>0.001172303144609563</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0003737698068288997</v>
+        <v>0.0003796312540870095</v>
       </c>
       <c r="CG8" t="n">
         <v>0.5148248255563884</v>
@@ -4375,7 +4375,7 @@
         <v>0.003284299383112985</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.006062084277657026</v>
+        <v>0.006030558426459046</v>
       </c>
       <c r="DQ8" t="n">
         <v>0.0005213376091990684</v>
@@ -4829,7 +4829,7 @@
         <v>0.0738564834242551</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.03281577843054969</v>
+        <v>0.03285774234158619</v>
       </c>
       <c r="DL9" t="n">
         <v>0.0008453085376162517</v>
@@ -4925,7 +4925,7 @@
         <v>0.002535925612848711</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.02647922786403688</v>
+        <v>0.02643726395300038</v>
       </c>
       <c r="ER9" t="n">
         <v>0.003592561284869</v>
@@ -4934,7 +4934,7 @@
         <v>0.001498127340823929</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.03279797125950975</v>
+        <v>0.03275570583262895</v>
       </c>
       <c r="EU9" t="n">
         <v>0.2407049937054133</v>
